--- a/artfynd/A 31438-2025 artfynd.xlsx
+++ b/artfynd/A 31438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128166239</v>
       </c>
       <c r="B2" t="n">
-        <v>79285</v>
+        <v>79288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2025 artfynd.xlsx
+++ b/artfynd/A 31438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128166239</v>
       </c>
       <c r="B2" t="n">
-        <v>79288</v>
+        <v>79339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2025 artfynd.xlsx
+++ b/artfynd/A 31438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128166239</v>
       </c>
       <c r="B2" t="n">
-        <v>79339</v>
+        <v>79343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31438-2025 artfynd.xlsx
+++ b/artfynd/A 31438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128166239</v>
       </c>
       <c r="B2" t="n">
-        <v>79343</v>
+        <v>79345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
